--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_22_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_22_IN_Piura.xlsx
@@ -1797,7 +1797,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>0.12</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="C11" s="21">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>6.59</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C12" s="30">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>73.53</v>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>19.76</v>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1914,11 +1914,11 @@
       </c>
       <c r="B15" s="43">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>79.3304</v>
       </c>
       <c r="C15" s="44">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
@@ -1939,11 +1939,11 @@
       </c>
       <c r="B16" s="46">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>5.3219</v>
       </c>
       <c r="C16" s="47">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>6.71</v>
       </c>
       <c r="D16" s="45" t="inlineStr">
         <is>
@@ -1964,11 +1964,11 @@
       </c>
       <c r="B17" s="46">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>74.0085</v>
       </c>
       <c r="C17" s="47">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>93.29</v>
       </c>
       <c r="D17" s="45" t="inlineStr">
         <is>
@@ -2162,11 +2162,11 @@
       </c>
       <c r="B29" s="22">
         <f>SUM(B25:B28)</f>
-        <v/>
+        <v>79.3737</v>
       </c>
       <c r="C29" s="23">
         <f>SUM(C25:C28)</f>
-        <v/>
+        <v>99.99</v>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
       <c r="E29" s="17" t="inlineStr"/>
@@ -2285,6 +2285,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2369,6 +2370,7 @@
       <c r="F11" s="17" t="inlineStr"/>
       <c r="G11" s="17" t="inlineStr"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -2417,6 +2419,7 @@
       <c r="G14" s="8" t="n"/>
       <c r="H14" s="8" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16" ht="120" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
@@ -2871,11 +2874,11 @@
       </c>
       <c r="B19" s="32">
         <f>SUM(B10:B18)</f>
-        <v/>
+        <v>875.24</v>
       </c>
       <c r="C19" s="23">
         <f>SUM(C10:C18)</f>
-        <v/>
+        <v>99.99</v>
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
@@ -2885,19 +2888,19 @@
       <c r="E19" s="17" t="inlineStr"/>
       <c r="F19" s="17">
         <f>ROUND(AVERAGE(F10:F18),2)</f>
-        <v/>
+        <v>22.85</v>
       </c>
       <c r="G19" s="22">
         <f>ROUND(AVERAGE(G10:G18),4)</f>
-        <v/>
+        <v>0.451</v>
       </c>
       <c r="H19" s="23">
         <f>ROUND(AVERAGE(H10:H18),2)</f>
-        <v/>
+        <v>29.59</v>
       </c>
       <c r="I19" s="23">
         <f>ROUND(AVERAGE(I10:I18),2)</f>
-        <v/>
+        <v>69.38</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1">
